--- a/data/asignaciones.xlsx
+++ b/data/asignaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sodexo-my.sharepoint.com/personal/andres_benavidesrodriguez_sodexo_com/Documents/Documents/proyecto_catalogo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{DAF8DC20-10C9-457E-A148-B63786AC149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C9AF6CA-A184-4FDA-84F9-236D874C15C0}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{DAF8DC20-10C9-457E-A148-B63786AC149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC43E170-668D-4673-8BB2-D9EB0788E266}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4936,8 +4936,8 @@
       <c r="C246" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="D246" s="4" t="s">
-        <v>9</v>
+      <c r="D246" s="8" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
